--- a/UnitySample/Assets/ExcelMaster/Data/Excels/ItemData.xlsx
+++ b/UnitySample/Assets/ExcelMaster/Data/Excels/ItemData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amaga\Documents\UnityProjects\ExcelMaster\UnitySample\Assets\ExcelMaster\Data\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3560B2B-2F06-482B-8381-7E786B1AAA5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE670CD-7CF1-48C4-BBBC-9D5E46C697C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -482,7 +482,7 @@
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="15.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="3.5" bestFit="1" customWidth="1"/>
@@ -493,7 +493,7 @@
     <col min="11" max="11" width="16.625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
